--- a/dentai-web/selenium-tests/reports/06_education_analytics_report.xlsx
+++ b/dentai-web/selenium-tests/reports/06_education_analytics_report.xlsx
@@ -443,7 +443,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:41:17 am</v>
+        <v>6/8/2026, 9:57:19 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -498,7 +498,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.50 seconds</v>
+        <v>1.45 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -639,10 +639,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -665,10 +665,10 @@
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -691,10 +691,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -717,10 +717,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -743,10 +743,10 @@
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -763,16 +763,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D7" t="str">
-        <v>WEB-SEL-256: Article Reading Time Estimate Badge</v>
+        <v>WEB-SEL-256: Article Reading Time Estimate Badge View</v>
       </c>
       <c r="E7" t="str">
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -789,16 +789,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D8" t="str">
-        <v>WEB-SEL-257: Bookmark Article for Offline Reading</v>
+        <v>WEB-SEL-257: Bookmark Article for Offline Reading Action</v>
       </c>
       <c r="E8" t="str">
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -815,16 +815,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D9" t="str">
-        <v>WEB-SEL-258: Remove Article from Bookmarks List</v>
+        <v>WEB-SEL-258: Remove Article from Bookmarks List Action</v>
       </c>
       <c r="E9" t="str">
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -847,10 +847,10 @@
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -873,10 +873,10 @@
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -899,10 +899,10 @@
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -925,10 +925,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -951,10 +951,10 @@
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -971,16 +971,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D15" t="str">
-        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card</v>
+        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card View</v>
       </c>
       <c r="E15" t="str">
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -997,16 +997,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D16" t="str">
-        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel</v>
+        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel Drag</v>
       </c>
       <c r="E16" t="str">
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1023,16 +1023,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D17" t="str">
-        <v>WEB-SEL-266: Download Patient Care Infographic PDF</v>
+        <v>WEB-SEL-266: Download Patient Care Infographic PDF Stream</v>
       </c>
       <c r="E17" t="str">
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1055,10 +1055,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1081,10 +1081,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1107,10 +1107,10 @@
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1133,10 +1133,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1159,10 +1159,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1211,10 +1211,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1237,10 +1237,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1257,16 +1257,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D26" t="str">
-        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets</v>
+        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets View</v>
       </c>
       <c r="E26" t="str">
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1289,10 +1289,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1315,10 +1315,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1335,16 +1335,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D29" t="str">
-        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week</v>
+        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week Chart</v>
       </c>
       <c r="E29" t="str">
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1361,16 +1361,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D30" t="str">
-        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart</v>
+        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart View</v>
       </c>
       <c r="E30" t="str">
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1387,16 +1387,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D31" t="str">
-        <v>WEB-SEL-280: High Risk Patient Alert Flag List</v>
+        <v>WEB-SEL-280: High Risk Patient Alert Flag List View</v>
       </c>
       <c r="E31" t="str">
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1419,10 +1419,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1445,10 +1445,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1465,16 +1465,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D34" t="str">
-        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance</v>
+        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance CSV</v>
       </c>
       <c r="E34" t="str">
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1491,16 +1491,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D35" t="str">
-        <v>WEB-SEL-284: Notification Center - Unread Alert Count</v>
+        <v>WEB-SEL-284: Notification Center - Unread Alert Count Badge</v>
       </c>
       <c r="E35" t="str">
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1523,10 +1523,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1543,16 +1543,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D37" t="str">
-        <v>WEB-SEL-286: Email Notification Frequency Selection</v>
+        <v>WEB-SEL-286: Email Notification Frequency Selection Dropdown</v>
       </c>
       <c r="E37" t="str">
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1575,10 +1575,10 @@
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1601,10 +1601,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1621,16 +1621,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D40" t="str">
-        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="E40" t="str">
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1647,16 +1647,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D41" t="str">
-        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="E41" t="str">
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1673,16 +1673,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D42" t="str">
-        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test</v>
+        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test Action</v>
       </c>
       <c r="E42" t="str">
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1705,10 +1705,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1731,10 +1731,10 @@
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1757,10 +1757,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1777,16 +1777,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D46" t="str">
-        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence</v>
+        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence Check</v>
       </c>
       <c r="E46" t="str">
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1803,16 +1803,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D47" t="str">
-        <v>WEB-SEL-296: Skip to Main Content Accessibility Link</v>
+        <v>WEB-SEL-296: Skip to Main Content Accessibility Link Test</v>
       </c>
       <c r="E47" t="str">
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1835,10 +1835,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1855,16 +1855,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D49" t="str">
-        <v>WEB-SEL-298: System Health Status Page Indicator</v>
+        <v>WEB-SEL-298: System Health Status Page Indicator View</v>
       </c>
       <c r="E49" t="str">
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1881,16 +1881,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D50" t="str">
-        <v>WEB-SEL-299: Feedback Rating Submission Form Modal</v>
+        <v>WEB-SEL-299: Feedback Rating Submission Form Modal Action</v>
       </c>
       <c r="E50" t="str">
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1907,16 +1907,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D51" t="str">
-        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal</v>
+        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal View</v>
       </c>
       <c r="E51" t="str">
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>
@@ -1979,10 +1979,10 @@
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -2002,10 +2002,10 @@
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -2025,10 +2025,10 @@
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -2048,10 +2048,10 @@
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -2071,10 +2071,10 @@
         <v>PASS</v>
       </c>
       <c r="E6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -2088,16 +2088,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C7" t="str">
-        <v>WEB-SEL-256: Article Reading Time Estimate Badge</v>
+        <v>WEB-SEL-256: Article Reading Time Estimate Badge View</v>
       </c>
       <c r="D7" t="str">
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -2111,16 +2111,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-257: Bookmark Article for Offline Reading</v>
+        <v>WEB-SEL-257: Bookmark Article for Offline Reading Action</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -2134,16 +2134,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C9" t="str">
-        <v>WEB-SEL-258: Remove Article from Bookmarks List</v>
+        <v>WEB-SEL-258: Remove Article from Bookmarks List Action</v>
       </c>
       <c r="D9" t="str">
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -2163,10 +2163,10 @@
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -2186,10 +2186,10 @@
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -2209,10 +2209,10 @@
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -2232,10 +2232,10 @@
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -2255,10 +2255,10 @@
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -2272,16 +2272,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C15" t="str">
-        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card</v>
+        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card View</v>
       </c>
       <c r="D15" t="str">
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -2295,16 +2295,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C16" t="str">
-        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel</v>
+        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel Drag</v>
       </c>
       <c r="D16" t="str">
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -2318,16 +2318,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-266: Download Patient Care Infographic PDF</v>
+        <v>WEB-SEL-266: Download Patient Care Infographic PDF Stream</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -2347,10 +2347,10 @@
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -2370,10 +2370,10 @@
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -2393,10 +2393,10 @@
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -2416,10 +2416,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -2439,10 +2439,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -2465,7 +2465,7 @@
         <v>21</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -2485,10 +2485,10 @@
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -2508,10 +2508,10 @@
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -2525,16 +2525,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets</v>
+        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets View</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -2554,10 +2554,10 @@
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -2577,10 +2577,10 @@
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -2594,16 +2594,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week</v>
+        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week Chart</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -2617,16 +2617,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C30" t="str">
-        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart</v>
+        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart View</v>
       </c>
       <c r="D30" t="str">
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -2640,16 +2640,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C31" t="str">
-        <v>WEB-SEL-280: High Risk Patient Alert Flag List</v>
+        <v>WEB-SEL-280: High Risk Patient Alert Flag List View</v>
       </c>
       <c r="D31" t="str">
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -2669,10 +2669,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -2692,10 +2692,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -2709,16 +2709,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C34" t="str">
-        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance</v>
+        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance CSV</v>
       </c>
       <c r="D34" t="str">
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -2732,16 +2732,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C35" t="str">
-        <v>WEB-SEL-284: Notification Center - Unread Alert Count</v>
+        <v>WEB-SEL-284: Notification Center - Unread Alert Count Badge</v>
       </c>
       <c r="D35" t="str">
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -2761,10 +2761,10 @@
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -2778,16 +2778,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C37" t="str">
-        <v>WEB-SEL-286: Email Notification Frequency Selection</v>
+        <v>WEB-SEL-286: Email Notification Frequency Selection Dropdown</v>
       </c>
       <c r="D37" t="str">
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -2807,10 +2807,10 @@
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -2847,16 +2847,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C40" t="str">
-        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="D40" t="str">
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -2870,16 +2870,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -2893,16 +2893,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test</v>
+        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test Action</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -2922,10 +2922,10 @@
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -2945,10 +2945,10 @@
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -2968,10 +2968,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -2985,16 +2985,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C46" t="str">
-        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence</v>
+        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence Check</v>
       </c>
       <c r="D46" t="str">
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -3008,16 +3008,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C47" t="str">
-        <v>WEB-SEL-296: Skip to Main Content Accessibility Link</v>
+        <v>WEB-SEL-296: Skip to Main Content Accessibility Link Test</v>
       </c>
       <c r="D47" t="str">
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -3037,10 +3037,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -3054,16 +3054,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-298: System Health Status Page Indicator</v>
+        <v>WEB-SEL-298: System Health Status Page Indicator View</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -3077,16 +3077,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C50" t="str">
-        <v>WEB-SEL-299: Feedback Rating Submission Form Modal</v>
+        <v>WEB-SEL-299: Feedback Rating Submission Form Modal Action</v>
       </c>
       <c r="D50" t="str">
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -3100,16 +3100,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C51" t="str">
-        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal</v>
+        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal View</v>
       </c>
       <c r="D51" t="str">
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
